--- a/AAII_Financials/Yearly/MDT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MDT_YR_FIN.xlsx
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45408</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45044</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44680</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44316</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43945</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43581</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43217</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42853</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42489</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42118</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41754</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41390</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41026</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36364000</v>
+      </c>
+      <c r="E8" s="3">
         <v>33537000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>32364000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31227000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>31686000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30117000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28913000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30557000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29953000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>29710000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28833000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20261000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17005000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16590000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16184000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12615000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11606000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11091000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10622000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10028000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10355000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9269000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9064000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9039000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9267000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9142000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6309000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4333000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8252000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3889000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>23749000</v>
+      </c>
+      <c r="E10" s="3">
         <v>21931000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21273000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20605000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21658000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19762000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19644000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21493000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20914000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20443000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19691000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13952000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12672000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8338000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12295000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,56 +903,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2873000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2732000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2735000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2696000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2746000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2493000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2331000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2330000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2256000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2193000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2224000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1640000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1477000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3114000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1490000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,105 +1002,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>875000</v>
+        <v>956000</v>
       </c>
       <c r="E14" s="3">
-        <v>1623000</v>
+        <v>1158000</v>
       </c>
       <c r="F14" s="3">
+        <v>1974000</v>
+      </c>
+      <c r="G14" s="3">
         <v>804000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1197000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>780000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>802000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>693000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>950000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>599000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>791000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1005000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>389000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>199000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>1807000</v>
+        <v>1893000</v>
       </c>
       <c r="E15" s="3">
+        <v>1958000</v>
+      </c>
+      <c r="F15" s="3">
         <v>1693000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1698000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1733000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1783000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1756000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1764000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1823000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1980000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1931000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>733000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>349000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>331000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>335000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27134000</v>
+        <v>29098000</v>
       </c>
       <c r="E17" s="3">
-        <v>25973000</v>
+        <v>27203000</v>
       </c>
       <c r="F17" s="3">
+        <v>25534000</v>
+      </c>
+      <c r="G17" s="3">
         <v>25658000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24839000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24627000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23751000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23848000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23408000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24327000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23472000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16285000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13177000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12162000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11890000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6403000</v>
+        <v>7266000</v>
       </c>
       <c r="E18" s="3">
-        <v>6391000</v>
+        <v>6334000</v>
       </c>
       <c r="F18" s="3">
+        <v>6830000</v>
+      </c>
+      <c r="G18" s="3">
         <v>5569000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6847000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5490000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5162000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6709000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6545000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5383000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5361000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3976000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3828000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4428000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4294000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1216,248 +1248,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-317000</v>
+        <v>-159000</v>
       </c>
       <c r="E20" s="3">
-        <v>-191000</v>
+        <v>-669000</v>
       </c>
       <c r="F20" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-796000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-234000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-110000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-787000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-625000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-76000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>313000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>361000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>176000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>256000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>211000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>8527000</v>
+        <v>9318000</v>
       </c>
       <c r="E21" s="3">
-        <v>8275000</v>
+        <v>8961000</v>
       </c>
       <c r="F21" s="3">
+        <v>8626000</v>
+      </c>
+      <c r="G21" s="3">
         <v>8063000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8814000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7383000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7705000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9098000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8444000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8613000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8542000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5458000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4934000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5327000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>715000</v>
+      </c>
+      <c r="E22" s="3">
         <v>729000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>719000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>583000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>553000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>925000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1092000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1444000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1146000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1094000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1386000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>666000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>379000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>388000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>349000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6137000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5627000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4837000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5364000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5517000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3895000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4055000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5197000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5675000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4602000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4336000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3486000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3705000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4251000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4145000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="E24" s="3">
         <v>936000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1133000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1580000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>456000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>265000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-751000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>547000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2580000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>578000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>798000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>811000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>640000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>784000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>730000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>4838000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4691000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3704000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3784000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5061000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3630000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4806000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4650000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3095000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4024000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3538000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2675000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3065000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3467000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3415000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>4801000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4662000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3676000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3758000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5039000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3606000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4789000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4631000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3104000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4028000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3538000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2675000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3065000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3467000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3415000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1647,9 +1704,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1677,8 +1737,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1686,18 +1746,21 @@
       <c r="N29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>202000</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,105 +1857,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>317000</v>
+        <v>159000</v>
       </c>
       <c r="E32" s="3">
-        <v>191000</v>
+        <v>669000</v>
       </c>
       <c r="F32" s="3">
+        <v>103000</v>
+      </c>
+      <c r="G32" s="3">
         <v>796000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>234000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>110000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>787000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>625000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>76000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-313000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-361000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-176000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-256000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-211000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4801000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4662000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3676000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3758000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5039000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3606000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4789000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4631000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3104000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4028000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3538000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2675000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3065000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3467000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3617000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4801000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4662000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3676000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3758000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5039000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3606000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4789000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4631000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3104000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4028000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3538000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2675000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3065000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3467000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3617000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E38" s="2">
         <v>45772</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45408</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45044</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44680</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44316</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43945</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43581</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43217</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42853</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42489</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42118</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41754</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41390</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41026</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,328 +2162,347 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1949000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2218000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1284000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1543000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3714000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3593000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4140000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4393000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3669000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4967000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2876000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4843000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2806000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>860000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1172000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7271000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6747000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6721000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6416000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6859000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7224000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6811000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5461000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7572000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8741000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9758000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14637000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>25676000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10211000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8178000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6643000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6515000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6128000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5998000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7650000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5462000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4645000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7951000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7913000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5591000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5562000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5112000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7622000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3727000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3808000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5951000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5476000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5217000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5293000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4616000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4313000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4229000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3753000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3579000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3338000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3473000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3463000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3450000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1712000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1800000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1813000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1808000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1755000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1540000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>695000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1426000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>359000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3933000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4423000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2789000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2866000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1283000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1378000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24787000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23814000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21935000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21675000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27702000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22548000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22031000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24084000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24974000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24873000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23600000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30844000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21210000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17793000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16336000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E47" s="3">
         <v>984000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1315000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1640000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>915000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>720000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>513000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>416000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>559000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>692000</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>24</v>
@@ -2406,111 +2510,120 @@
       <c r="O47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="3">
         <v>549000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>508000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8614000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7937000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7143000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6610000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6267000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6219000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5755000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4042000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4071000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4361000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14555000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4699000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4784000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2490000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2473000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>52733000</v>
+      </c>
+      <c r="E49" s="3">
         <v>53404000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>54211000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>56269000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>56097000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59701000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>58904000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>61152000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>61799000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>61922000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>68399000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>68631000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25758000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13002000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12581000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,57 +2720,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2093000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1501000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1720000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1277000</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>726000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>654000</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M52" s="3">
         <v>8009000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2804000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2511000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2924000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1007000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>920000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>93028000</v>
+      </c>
+      <c r="E54" s="3">
         <v>91680000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>89981000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90948000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>90981000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>93083000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90689000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>89694000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>91403000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99857000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99644000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106685000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>37943000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34841000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32818000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,296 +2918,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2644000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2449000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2410000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2662000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2276000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2106000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1996000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1953000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1628000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1555000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1709000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1610000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1484000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>622000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>565000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1986000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3066000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1275000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>200000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3909000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>197000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2947000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>838000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2058000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7520000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1986000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2424000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3202000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>910000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3274000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1965000</v>
+        <v>1614000</v>
       </c>
       <c r="E59" s="3">
+        <v>1949000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1827000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1306000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2544000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>990000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>867000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1772000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1362000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5189000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4463000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5139000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6432000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2359000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2088000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11658000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12879000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10789000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9051000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10823000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8509000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10366000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6987000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8363000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14264000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7165000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9173000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5559000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3891000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5927000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27163000</v>
+      </c>
+      <c r="E61" s="3">
         <v>26560000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>24772000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25213000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21075000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27207000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22795000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24486000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23719000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25921000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30109000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>33752000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10315000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9741000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7359000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3184000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2980000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2919000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3742000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4284000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4644000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5392000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5000000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5671000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8622000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10307000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10530000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5252000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2538000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2419000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42956000</v>
+      </c>
+      <c r="E66" s="3">
         <v>43424000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39561000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39283000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38259000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41481000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39817000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>39482000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40674000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49649000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47581000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53455000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18500000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16170000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15705000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32638000</v>
+      </c>
+      <c r="E72" s="3">
         <v>31476000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30403000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30392000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16849000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28594000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28132000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16098000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16632000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23270000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21704000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>54414000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39880000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19061000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17482000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49463000</v>
+      </c>
+      <c r="E76" s="3">
         <v>48024000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50214000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51483000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>52551000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51428000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50737000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>50091000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50627000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>50208000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52063000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53230000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19443000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18671000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17113000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46136</v>
+      </c>
+      <c r="E80" s="2">
         <v>45772</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45408</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45044</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44680</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44316</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43945</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43581</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43217</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42853</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42489</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42118</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41754</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41390</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41026</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4801000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4662000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3676000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3758000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5039000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3606000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4789000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4631000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3104000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4028000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3538000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2675000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3065000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3467000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3617000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1054000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>954000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>999000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>974000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>919000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>907000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>895000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>821000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2917000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2820000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1306000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>850000</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>833000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7330000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7044000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6787000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6039000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7346000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6240000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7234000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7007000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4684000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6880000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5218000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4902000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4959000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4942000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4470000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1904000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1859000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1459000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1368000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1213000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1134000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1068000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1254000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1046000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-571000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-396000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-457000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-484000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2934000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1937000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2366000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3493000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1659000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2866000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3203000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-774000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5858000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1571000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2245000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17058000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3594000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2662000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,56 +4690,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3639000</v>
+      </c>
+      <c r="E96" s="3">
         <v>3589000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3666000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3616000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3383000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3120000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2894000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2693000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2494000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2376000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2139000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1337000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1116000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1055000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1021000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,151 +4891,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4751000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4361000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4450000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4960000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5336000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4136000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4198000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5431000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11954000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3283000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9543000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15949000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-918000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1882000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E101" s="3">
         <v>188000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-230000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>243000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-231000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>215000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-86000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-78000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>114000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>65000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>113000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-353000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>37000</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-71000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-270000</v>
+      </c>
+      <c r="E102" s="3">
         <v>934000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-259000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2171000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>120000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-547000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-253000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>724000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1298000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2091000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1967000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3440000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>484000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-253000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-145000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
